--- a/Data/Invoice_conf_scores.xlsx
+++ b/Data/Invoice_conf_scores.xlsx
@@ -65,16 +65,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -90,7 +82,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -98,30 +90,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,54 +394,54 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
@@ -517,7 +491,7 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
@@ -567,7 +541,7 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
@@ -617,7 +591,7 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
@@ -667,7 +641,7 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
@@ -717,7 +691,7 @@
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
@@ -767,7 +741,7 @@
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
@@ -817,7 +791,7 @@
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
@@ -867,7 +841,7 @@
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
@@ -917,7 +891,7 @@
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
@@ -967,7 +941,7 @@
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
@@ -1017,7 +991,7 @@
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>11</v>
       </c>
       <c r="B13">
